--- a/leetcode/dptable.xlsx
+++ b/leetcode/dptable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="13220"/>
+    <workbookView windowWidth="28000" windowHeight="12580"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16">
   <si>
     <t>[]</t>
   </si>
@@ -45,14 +45,32 @@
   <si>
     <t>[1, 2, 3, 4]</t>
   </si>
+  <si>
+    <t>""</t>
+  </si>
+  <si>
+    <t>a</t>
+  </si>
+  <si>
+    <t>b</t>
+  </si>
+  <si>
+    <t>c</t>
+  </si>
+  <si>
+    <t>d</t>
+  </si>
+  <si>
+    <t>e</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="177" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
@@ -71,17 +89,11 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -93,6 +105,94 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
@@ -102,21 +202,23 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF3F3F3F"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -130,59 +232,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -190,37 +239,6 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="34">
     <fill>
@@ -249,37 +267,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -291,25 +321,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -321,13 +417,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -339,85 +435,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -483,6 +501,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -503,15 +530,6 @@
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -540,17 +558,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -570,13 +584,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FFB2B2B2"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -585,152 +603,152 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="12" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -767,6 +785,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="18" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -774,6 +795,12 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="42" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="42" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="42" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="18" applyFont="1" applyFill="1" applyBorder="1">
@@ -1155,30 +1182,30 @@
         <v>11</v>
       </c>
       <c r="P2" s="10"/>
-      <c r="Q2" s="12">
-        <v>0</v>
-      </c>
-      <c r="R2" s="12">
-        <v>1</v>
-      </c>
-      <c r="S2" s="12">
+      <c r="Q2" s="13">
+        <v>0</v>
+      </c>
+      <c r="R2" s="13">
+        <v>1</v>
+      </c>
+      <c r="S2" s="13">
         <v>2</v>
       </c>
-      <c r="T2" s="12">
+      <c r="T2" s="13">
         <v>3</v>
       </c>
-      <c r="U2" s="12">
+      <c r="U2" s="13">
         <v>4</v>
       </c>
-      <c r="V2" s="12">
+      <c r="V2" s="13">
         <v>5</v>
       </c>
-      <c r="W2" s="15"/>
-      <c r="X2" s="15"/>
-      <c r="Y2" s="15"/>
-      <c r="Z2" s="15"/>
-      <c r="AA2" s="15"/>
-      <c r="AB2" s="15"/>
+      <c r="W2" s="18"/>
+      <c r="X2" s="18"/>
+      <c r="Y2" s="18"/>
+      <c r="Z2" s="18"/>
+      <c r="AA2" s="18"/>
+      <c r="AB2" s="18"/>
     </row>
     <row r="3" spans="2:28">
       <c r="B3" s="3" t="s">
@@ -1241,12 +1268,12 @@
       <c r="V3" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="W3" s="16"/>
-      <c r="X3" s="16"/>
-      <c r="Y3" s="16"/>
-      <c r="Z3" s="16"/>
-      <c r="AA3" s="16"/>
-      <c r="AB3" s="16"/>
+      <c r="W3" s="19"/>
+      <c r="X3" s="19"/>
+      <c r="Y3" s="19"/>
+      <c r="Z3" s="19"/>
+      <c r="AA3" s="19"/>
+      <c r="AB3" s="19"/>
     </row>
     <row r="4" spans="2:28">
       <c r="B4" s="3" t="s">
@@ -1267,28 +1294,28 @@
       <c r="P4" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="Q4" s="13"/>
-      <c r="R4" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="S4" s="14" t="s">
+      <c r="Q4" s="14"/>
+      <c r="R4" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="S4" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="T4" s="14" t="s">
+      <c r="T4" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="U4" s="14" t="s">
+      <c r="U4" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="V4" s="14" t="s">
+      <c r="V4" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="W4" s="17"/>
-      <c r="X4" s="17"/>
-      <c r="Y4" s="17"/>
-      <c r="Z4" s="17"/>
-      <c r="AA4" s="17"/>
-      <c r="AB4" s="17"/>
+      <c r="W4" s="20"/>
+      <c r="X4" s="20"/>
+      <c r="Y4" s="20"/>
+      <c r="Z4" s="20"/>
+      <c r="AA4" s="20"/>
+      <c r="AB4" s="20"/>
     </row>
     <row r="5" spans="2:28">
       <c r="B5" s="3" t="s">
@@ -1309,18 +1336,18 @@
       <c r="P5" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="Q5" s="14"/>
-      <c r="R5" s="14"/>
-      <c r="S5" s="14"/>
-      <c r="T5" s="14"/>
-      <c r="U5" s="14"/>
-      <c r="V5" s="14"/>
-      <c r="W5" s="17"/>
-      <c r="X5" s="17"/>
-      <c r="Y5" s="17"/>
-      <c r="Z5" s="17"/>
-      <c r="AA5" s="17"/>
-      <c r="AB5" s="17"/>
+      <c r="Q5" s="15"/>
+      <c r="R5" s="15"/>
+      <c r="S5" s="15"/>
+      <c r="T5" s="15"/>
+      <c r="U5" s="15"/>
+      <c r="V5" s="15"/>
+      <c r="W5" s="20"/>
+      <c r="X5" s="20"/>
+      <c r="Y5" s="20"/>
+      <c r="Z5" s="20"/>
+      <c r="AA5" s="20"/>
+      <c r="AB5" s="20"/>
     </row>
     <row r="6" spans="2:28">
       <c r="B6" s="3" t="s">
@@ -1341,29 +1368,29 @@
       <c r="P6" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="Q6" s="14"/>
-      <c r="R6" s="14"/>
-      <c r="S6" s="14"/>
-      <c r="T6" s="14"/>
-      <c r="U6" s="14"/>
-      <c r="V6" s="14"/>
-      <c r="W6" s="17"/>
-      <c r="X6" s="17"/>
-      <c r="Y6" s="17"/>
-      <c r="Z6" s="17"/>
-      <c r="AA6" s="17"/>
-      <c r="AB6" s="17"/>
+      <c r="Q6" s="15"/>
+      <c r="R6" s="15"/>
+      <c r="S6" s="15"/>
+      <c r="T6" s="15"/>
+      <c r="U6" s="15"/>
+      <c r="V6" s="15"/>
+      <c r="W6" s="20"/>
+      <c r="X6" s="20"/>
+      <c r="Y6" s="20"/>
+      <c r="Z6" s="20"/>
+      <c r="AA6" s="20"/>
+      <c r="AB6" s="20"/>
     </row>
     <row r="7" spans="16:22">
       <c r="P7" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="Q7" s="14"/>
-      <c r="R7" s="14"/>
-      <c r="S7" s="14"/>
-      <c r="T7" s="14"/>
-      <c r="U7" s="14"/>
-      <c r="V7" s="14"/>
+      <c r="Q7" s="15"/>
+      <c r="R7" s="15"/>
+      <c r="S7" s="15"/>
+      <c r="T7" s="15"/>
+      <c r="U7" s="15"/>
+      <c r="V7" s="15"/>
     </row>
     <row r="8" spans="2:14">
       <c r="B8" s="2"/>
@@ -1404,7 +1431,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="2:14">
+    <row r="9" spans="2:22">
       <c r="B9" s="3" t="s">
         <v>0</v>
       </c>
@@ -1444,8 +1471,27 @@
       <c r="N9" s="3">
         <v>0</v>
       </c>
+      <c r="P9" s="10"/>
+      <c r="Q9" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="R9" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="S9" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="T9" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="U9" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="V9" s="13" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="10" spans="2:14">
+    <row r="10" spans="2:22">
       <c r="B10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1481,8 +1527,29 @@
       <c r="N10" s="8">
         <v>0</v>
       </c>
+      <c r="P10" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q10" s="8">
+        <v>0</v>
+      </c>
+      <c r="R10" s="8">
+        <v>0</v>
+      </c>
+      <c r="S10" s="8">
+        <v>0</v>
+      </c>
+      <c r="T10" s="8">
+        <v>0</v>
+      </c>
+      <c r="U10" s="8">
+        <v>0</v>
+      </c>
+      <c r="V10" s="8">
+        <v>0</v>
+      </c>
     </row>
-    <row r="11" spans="2:14">
+    <row r="11" spans="2:22">
       <c r="B11" s="3" t="s">
         <v>5</v>
       </c>
@@ -1498,8 +1565,19 @@
       <c r="L11" s="9"/>
       <c r="M11" s="9"/>
       <c r="N11" s="9"/>
+      <c r="P11" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q11" s="16">
+        <v>0</v>
+      </c>
+      <c r="R11" s="15"/>
+      <c r="S11" s="15"/>
+      <c r="T11" s="15"/>
+      <c r="U11" s="15"/>
+      <c r="V11" s="15"/>
     </row>
-    <row r="12" spans="2:14">
+    <row r="12" spans="2:22">
       <c r="B12" s="3" t="s">
         <v>7</v>
       </c>
@@ -1515,8 +1593,32 @@
       <c r="L12" s="4"/>
       <c r="M12" s="9"/>
       <c r="N12" s="9"/>
+      <c r="P12" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q12" s="15">
+        <v>0</v>
+      </c>
+      <c r="R12" s="15"/>
+      <c r="S12" s="15"/>
+      <c r="T12" s="15"/>
+      <c r="U12" s="15"/>
+      <c r="V12" s="15"/>
     </row>
-    <row r="14" spans="2:14">
+    <row r="13" spans="16:22">
+      <c r="P13" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q13" s="15">
+        <v>0</v>
+      </c>
+      <c r="R13" s="15"/>
+      <c r="S13" s="15"/>
+      <c r="T13" s="15"/>
+      <c r="U13" s="15"/>
+      <c r="V13" s="15"/>
+    </row>
+    <row r="14" spans="2:22">
       <c r="B14" s="2"/>
       <c r="C14" s="2">
         <v>0</v>
@@ -1554,6 +1656,13 @@
       <c r="N14" s="2">
         <v>11</v>
       </c>
+      <c r="P14" s="12"/>
+      <c r="Q14" s="17"/>
+      <c r="R14" s="17"/>
+      <c r="S14" s="17"/>
+      <c r="T14" s="17"/>
+      <c r="U14" s="17"/>
+      <c r="V14" s="17"/>
     </row>
     <row r="15" spans="2:14">
       <c r="B15" s="3" t="s">

--- a/leetcode/dptable.xlsx
+++ b/leetcode/dptable.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19">
   <si>
     <t>[]</t>
   </si>
@@ -63,18 +63,27 @@
   <si>
     <t>e</t>
   </si>
+  <si>
+    <t>abcbe</t>
+  </si>
+  <si>
+    <t>题解</t>
+  </si>
+  <si>
+    <t>s[i]!=s[j]</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="24">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -89,6 +98,109 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Apple Symbols"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="圆体-简"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="15"/>
       <color theme="3"/>
@@ -99,44 +211,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF9C6500"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -144,29 +226,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -176,59 +236,6 @@
       <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -239,6 +246,20 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="34">
     <fill>
@@ -267,13 +288,133 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -285,157 +426,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -510,21 +531,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -549,22 +555,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FFB2B2B2"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -584,17 +585,37 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -603,127 +624,127 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="12" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -735,20 +756,20 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -797,12 +818,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="42" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="42" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="42" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="42" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="18" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -811,6 +832,15 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="42" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="18" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1131,14 +1161,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr/>
-  <dimension ref="B2:AB18"/>
+  <dimension ref="B2:AB21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="2" width="10.8308823529412" style="1"/>
     <col min="3" max="14" width="3.83088235294118" style="1" customWidth="1"/>
     <col min="15" max="15" width="10.8308823529412" style="1"/>
-    <col min="16" max="16" width="10.6617647058824" style="1" customWidth="1"/>
-    <col min="17" max="26" width="3.16176470588235" style="1" customWidth="1"/>
+    <col min="16" max="16" width="5.65441176470588" style="1" customWidth="1"/>
+    <col min="17" max="21" width="6.64705882352941" style="1" customWidth="1"/>
+    <col min="22" max="26" width="3.16176470588235" style="1" customWidth="1"/>
     <col min="27" max="28" width="4.33088235294118" style="1" customWidth="1"/>
     <col min="29" max="16384" width="10.8308823529412" style="1"/>
   </cols>
@@ -1568,7 +1599,7 @@
       <c r="P11" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="Q11" s="16">
+      <c r="Q11" s="15">
         <v>0</v>
       </c>
       <c r="R11" s="15"/>
@@ -1657,14 +1688,14 @@
         <v>11</v>
       </c>
       <c r="P14" s="12"/>
-      <c r="Q14" s="17"/>
-      <c r="R14" s="17"/>
-      <c r="S14" s="17"/>
-      <c r="T14" s="17"/>
-      <c r="U14" s="17"/>
-      <c r="V14" s="17"/>
+      <c r="Q14" s="16"/>
+      <c r="R14" s="16"/>
+      <c r="S14" s="16"/>
+      <c r="T14" s="16"/>
+      <c r="U14" s="16"/>
+      <c r="V14" s="16"/>
     </row>
-    <row r="15" spans="2:14">
+    <row r="15" spans="2:22">
       <c r="B15" s="3" t="s">
         <v>0</v>
       </c>
@@ -1704,8 +1735,27 @@
       <c r="N15" s="3">
         <v>0</v>
       </c>
+      <c r="P15" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q15" s="13">
+        <v>0</v>
+      </c>
+      <c r="R15" s="13">
+        <v>1</v>
+      </c>
+      <c r="S15" s="13">
+        <v>2</v>
+      </c>
+      <c r="T15" s="13">
+        <v>3</v>
+      </c>
+      <c r="U15" s="13">
+        <v>4</v>
+      </c>
+      <c r="V15" s="21"/>
     </row>
-    <row r="16" spans="2:14">
+    <row r="16" spans="2:22">
       <c r="B16" s="3" t="s">
         <v>3</v>
       </c>
@@ -1741,8 +1791,21 @@
       <c r="N16" s="8">
         <v>0</v>
       </c>
+      <c r="P16" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="8">
+        <v>1</v>
+      </c>
+      <c r="R16" s="8"/>
+      <c r="S16" s="8"/>
+      <c r="T16" s="8"/>
+      <c r="U16" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="V16" s="23"/>
     </row>
-    <row r="17" spans="2:14">
+    <row r="17" spans="2:22">
       <c r="B17" s="3" t="s">
         <v>5</v>
       </c>
@@ -1772,8 +1835,21 @@
       <c r="N17" s="8">
         <v>1</v>
       </c>
+      <c r="P17" s="11">
+        <v>1</v>
+      </c>
+      <c r="Q17" s="15"/>
+      <c r="R17" s="15">
+        <v>1</v>
+      </c>
+      <c r="S17" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="T17" s="17"/>
+      <c r="U17" s="15"/>
+      <c r="V17" s="16"/>
     </row>
-    <row r="18" spans="2:14">
+    <row r="18" spans="2:22">
       <c r="B18" s="3" t="s">
         <v>7</v>
       </c>
@@ -1793,6 +1869,52 @@
       <c r="N18" s="8">
         <v>1</v>
       </c>
+      <c r="P18" s="11">
+        <v>2</v>
+      </c>
+      <c r="Q18" s="15"/>
+      <c r="R18" s="3"/>
+      <c r="S18" s="15">
+        <v>1</v>
+      </c>
+      <c r="T18" s="15"/>
+      <c r="U18" s="15"/>
+      <c r="V18" s="16"/>
+    </row>
+    <row r="19" spans="16:22">
+      <c r="P19" s="11">
+        <v>3</v>
+      </c>
+      <c r="Q19" s="15"/>
+      <c r="R19" s="3"/>
+      <c r="S19" s="15"/>
+      <c r="T19" s="15">
+        <v>1</v>
+      </c>
+      <c r="U19" s="15"/>
+      <c r="V19" s="16"/>
+    </row>
+    <row r="20" spans="16:22">
+      <c r="P20" s="11">
+        <v>4</v>
+      </c>
+      <c r="Q20" s="15"/>
+      <c r="R20" s="15"/>
+      <c r="S20" s="15"/>
+      <c r="T20" s="15"/>
+      <c r="U20" s="15">
+        <v>1</v>
+      </c>
+      <c r="V20" s="16"/>
+    </row>
+    <row r="21" spans="16:22">
+      <c r="P21" s="12"/>
+      <c r="Q21" s="16"/>
+      <c r="R21" s="16"/>
+      <c r="S21" s="16"/>
+      <c r="T21" s="16"/>
+      <c r="U21" s="16"/>
+      <c r="V21" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="4">

--- a/leetcode/dptable.xlsx
+++ b/leetcode/dptable.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20">
   <si>
     <t>[]</t>
   </si>
@@ -72,15 +72,18 @@
   <si>
     <t>s[i]!=s[j]</t>
   </si>
+  <si>
+    <t>cbbd</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="24">
@@ -118,6 +121,72 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
       <name val="Calibri"/>
       <charset val="0"/>
@@ -125,7 +194,39 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -139,29 +240,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
@@ -170,16 +248,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -192,74 +263,6 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="34">
     <fill>
@@ -288,175 +291,175 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -570,6 +573,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -581,17 +593,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -613,9 +614,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -624,152 +627,152 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="24" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -840,6 +843,12 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="18" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1161,7 +1170,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr/>
-  <dimension ref="B2:AB21"/>
+  <dimension ref="B2:AB27"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="2" width="10.8308823529412" style="1"/>
@@ -1916,6 +1925,82 @@
       <c r="U21" s="16"/>
       <c r="V21" s="16"/>
     </row>
+    <row r="22" spans="16:21">
+      <c r="P22" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q22" s="13">
+        <v>0</v>
+      </c>
+      <c r="R22" s="13">
+        <v>1</v>
+      </c>
+      <c r="S22" s="13">
+        <v>2</v>
+      </c>
+      <c r="T22" s="13">
+        <v>3</v>
+      </c>
+      <c r="U22" s="24"/>
+    </row>
+    <row r="23" spans="16:21">
+      <c r="P23" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="R23" s="8"/>
+      <c r="S23" s="8"/>
+      <c r="T23" s="8"/>
+      <c r="U23" s="25"/>
+    </row>
+    <row r="24" spans="16:21">
+      <c r="P24" s="11">
+        <v>1</v>
+      </c>
+      <c r="Q24" s="15"/>
+      <c r="R24" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="S24" s="17"/>
+      <c r="T24" s="17"/>
+      <c r="U24" s="16"/>
+    </row>
+    <row r="25" spans="16:21">
+      <c r="P25" s="11">
+        <v>2</v>
+      </c>
+      <c r="Q25" s="15"/>
+      <c r="R25" s="3"/>
+      <c r="S25" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="T25" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="U25" s="16"/>
+    </row>
+    <row r="26" spans="16:21">
+      <c r="P26" s="11">
+        <v>3</v>
+      </c>
+      <c r="Q26" s="15"/>
+      <c r="R26" s="3"/>
+      <c r="S26" s="15"/>
+      <c r="T26" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="U26" s="16"/>
+    </row>
+    <row r="27" spans="16:21">
+      <c r="P27" s="12"/>
+      <c r="Q27" s="16"/>
+      <c r="R27" s="16"/>
+      <c r="S27" s="16"/>
+      <c r="T27" s="16"/>
+      <c r="U27" s="16"/>
+    </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="C10:D10"/>

--- a/leetcode/dptable.xlsx
+++ b/leetcode/dptable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28000" windowHeight="12580"/>
+    <workbookView windowWidth="28800" windowHeight="12580"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22">
   <si>
     <t>[]</t>
   </si>
@@ -25,19 +25,13 @@
     <t>F</t>
   </si>
   <si>
-    <t>[2]</t>
-  </si>
-  <si>
     <t>[1]</t>
-  </si>
-  <si>
-    <t>[2, 5]</t>
   </si>
   <si>
     <t>[1, 2]</t>
   </si>
   <si>
-    <t>[2, 5, 10]</t>
+    <t>[1, 2, 5]</t>
   </si>
   <si>
     <t>[1, 2, 3]</t>
@@ -64,6 +58,15 @@
     <t>e</t>
   </si>
   <si>
+    <t>[2]</t>
+  </si>
+  <si>
+    <t>[2, 5]</t>
+  </si>
+  <si>
+    <t>[2, 5, 10]</t>
+  </si>
+  <si>
     <t>abcbe</t>
   </si>
   <si>
@@ -75,16 +78,19 @@
   <si>
     <t>cbbd</t>
   </si>
+  <si>
+    <t>4*4</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -120,8 +126,101 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -136,25 +235,9 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -166,13 +249,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="Calibri"/>
       <charset val="0"/>
@@ -180,77 +256,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -291,19 +297,151 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -315,151 +453,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -558,26 +564,17 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -597,21 +594,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -622,157 +604,181 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="24" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="12" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -785,12 +791,18 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="42" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="42" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="42" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="42" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="42" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="42" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -843,9 +855,6 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="18" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1170,15 +1179,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr/>
-  <dimension ref="B2:AB27"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <dimension ref="B2:AB34"/>
+  <sheetFormatPr defaultColWidth="4.64705882352941" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="2" width="10.8308823529412" style="1"/>
     <col min="3" max="14" width="3.83088235294118" style="1" customWidth="1"/>
     <col min="15" max="15" width="10.8308823529412" style="1"/>
     <col min="16" max="16" width="5.65441176470588" style="1" customWidth="1"/>
-    <col min="17" max="21" width="6.64705882352941" style="1" customWidth="1"/>
-    <col min="22" max="26" width="3.16176470588235" style="1" customWidth="1"/>
+    <col min="17" max="22" width="4.64705882352941" style="1" customWidth="1"/>
+    <col min="23" max="26" width="3.16176470588235" style="1" customWidth="1"/>
     <col min="27" max="28" width="4.33088235294118" style="1" customWidth="1"/>
     <col min="29" max="16384" width="10.8308823529412" style="1"/>
   </cols>
@@ -1221,216 +1230,266 @@
       <c r="N2" s="2">
         <v>11</v>
       </c>
-      <c r="P2" s="10"/>
-      <c r="Q2" s="13">
-        <v>0</v>
-      </c>
-      <c r="R2" s="13">
-        <v>1</v>
-      </c>
-      <c r="S2" s="13">
-        <v>2</v>
-      </c>
-      <c r="T2" s="13">
+      <c r="P2" s="12"/>
+      <c r="Q2" s="15">
+        <v>0</v>
+      </c>
+      <c r="R2" s="15">
+        <v>1</v>
+      </c>
+      <c r="S2" s="15">
+        <v>2</v>
+      </c>
+      <c r="T2" s="15">
         <v>3</v>
       </c>
-      <c r="U2" s="13">
+      <c r="U2" s="15">
         <v>4</v>
       </c>
-      <c r="V2" s="13">
+      <c r="V2" s="15">
         <v>5</v>
       </c>
-      <c r="W2" s="18"/>
-      <c r="X2" s="18"/>
-      <c r="Y2" s="18"/>
-      <c r="Z2" s="18"/>
-      <c r="AA2" s="18"/>
-      <c r="AB2" s="18"/>
+      <c r="W2" s="20"/>
+      <c r="X2" s="20"/>
+      <c r="Y2" s="20"/>
+      <c r="Z2" s="20"/>
+      <c r="AA2" s="20"/>
+      <c r="AB2" s="20"/>
     </row>
     <row r="3" spans="2:28">
       <c r="B3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C3" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E3" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="F3" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G3" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H3" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I3" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J3" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K3" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L3" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="M3" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N3" s="3">
-        <v>0</v>
-      </c>
-      <c r="P3" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="R3" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="S3" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="T3" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="U3" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="V3" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="W3" s="19"/>
-      <c r="X3" s="19"/>
-      <c r="Y3" s="19"/>
-      <c r="Z3" s="19"/>
-      <c r="AA3" s="19"/>
-      <c r="AB3" s="19"/>
+        <v>-1</v>
+      </c>
+      <c r="P3" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="R3" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="S3" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="T3" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="U3" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="V3" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="W3" s="21"/>
+      <c r="X3" s="21"/>
+      <c r="Y3" s="21"/>
+      <c r="Z3" s="21"/>
+      <c r="AA3" s="21"/>
+      <c r="AB3" s="21"/>
     </row>
     <row r="4" spans="2:28">
       <c r="B4" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
-      <c r="M4" s="4"/>
-      <c r="N4" s="4"/>
-      <c r="P4" s="11" t="s">
+      <c r="D4" s="3">
+        <v>1</v>
+      </c>
+      <c r="E4" s="10">
+        <v>2</v>
+      </c>
+      <c r="F4" s="10">
+        <v>3</v>
+      </c>
+      <c r="G4" s="10">
         <v>4</v>
       </c>
-      <c r="Q4" s="14"/>
-      <c r="R4" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="S4" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="T4" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="U4" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="V4" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="W4" s="20"/>
-      <c r="X4" s="20"/>
-      <c r="Y4" s="20"/>
-      <c r="Z4" s="20"/>
-      <c r="AA4" s="20"/>
-      <c r="AB4" s="20"/>
+      <c r="H4" s="10">
+        <v>5</v>
+      </c>
+      <c r="I4" s="10">
+        <v>6</v>
+      </c>
+      <c r="J4" s="10">
+        <v>7</v>
+      </c>
+      <c r="K4" s="10">
+        <v>8</v>
+      </c>
+      <c r="L4" s="10">
+        <v>9</v>
+      </c>
+      <c r="M4" s="10">
+        <v>10</v>
+      </c>
+      <c r="N4" s="10">
+        <v>11</v>
+      </c>
+      <c r="P4" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q4" s="16"/>
+      <c r="R4" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="S4" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="T4" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="U4" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="V4" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="W4" s="22"/>
+      <c r="X4" s="22"/>
+      <c r="Y4" s="22"/>
+      <c r="Z4" s="22"/>
+      <c r="AA4" s="22"/>
+      <c r="AB4" s="22"/>
     </row>
     <row r="5" spans="2:28">
       <c r="B5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="3">
+        <v>1</v>
+      </c>
+      <c r="F5" s="3">
+        <v>2</v>
+      </c>
+      <c r="G5" s="3">
+        <v>2</v>
+      </c>
+      <c r="H5" s="11">
+        <v>3</v>
+      </c>
+      <c r="I5" s="11">
+        <v>3</v>
+      </c>
+      <c r="J5" s="11">
+        <v>4</v>
+      </c>
+      <c r="K5" s="11">
+        <v>4</v>
+      </c>
+      <c r="L5" s="11">
         <v>5</v>
       </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
-      <c r="K5" s="4"/>
-      <c r="L5" s="4"/>
-      <c r="M5" s="4"/>
-      <c r="N5" s="4"/>
-      <c r="P5" s="11" t="s">
+      <c r="M5" s="11">
+        <v>5</v>
+      </c>
+      <c r="N5" s="11">
         <v>6</v>
       </c>
-      <c r="Q5" s="15"/>
-      <c r="R5" s="15"/>
-      <c r="S5" s="15"/>
-      <c r="T5" s="15"/>
-      <c r="U5" s="15"/>
-      <c r="V5" s="15"/>
-      <c r="W5" s="20"/>
-      <c r="X5" s="20"/>
-      <c r="Y5" s="20"/>
-      <c r="Z5" s="20"/>
-      <c r="AA5" s="20"/>
-      <c r="AB5" s="20"/>
+      <c r="P5" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q5" s="17"/>
+      <c r="R5" s="17"/>
+      <c r="S5" s="17"/>
+      <c r="T5" s="17"/>
+      <c r="U5" s="17"/>
+      <c r="V5" s="17"/>
+      <c r="W5" s="22"/>
+      <c r="X5" s="22"/>
+      <c r="Y5" s="22"/>
+      <c r="Z5" s="22"/>
+      <c r="AA5" s="22"/>
+      <c r="AB5" s="22"/>
     </row>
     <row r="6" spans="2:28">
       <c r="B6" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="6"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="10">
+        <v>1</v>
+      </c>
+      <c r="I6" s="10">
+        <v>2</v>
+      </c>
+      <c r="J6" s="10">
+        <v>2</v>
+      </c>
+      <c r="K6" s="10">
+        <v>3</v>
+      </c>
+      <c r="L6" s="10"/>
+      <c r="M6" s="11"/>
+      <c r="N6" s="11"/>
+      <c r="P6" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q6" s="17"/>
+      <c r="R6" s="17"/>
+      <c r="S6" s="17"/>
+      <c r="T6" s="17"/>
+      <c r="U6" s="17"/>
+      <c r="V6" s="17"/>
+      <c r="W6" s="22"/>
+      <c r="X6" s="22"/>
+      <c r="Y6" s="22"/>
+      <c r="Z6" s="22"/>
+      <c r="AA6" s="22"/>
+      <c r="AB6" s="22"/>
+    </row>
+    <row r="7" spans="16:22">
+      <c r="P7" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
-      <c r="K6" s="4"/>
-      <c r="L6" s="4"/>
-      <c r="M6" s="4"/>
-      <c r="N6" s="4"/>
-      <c r="P6" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q6" s="15"/>
-      <c r="R6" s="15"/>
-      <c r="S6" s="15"/>
-      <c r="T6" s="15"/>
-      <c r="U6" s="15"/>
-      <c r="V6" s="15"/>
-      <c r="W6" s="20"/>
-      <c r="X6" s="20"/>
-      <c r="Y6" s="20"/>
-      <c r="Z6" s="20"/>
-      <c r="AA6" s="20"/>
-      <c r="AB6" s="20"/>
-    </row>
-    <row r="7" spans="16:22">
-      <c r="P7" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q7" s="15"/>
-      <c r="R7" s="15"/>
-      <c r="S7" s="15"/>
-      <c r="T7" s="15"/>
-      <c r="U7" s="15"/>
-      <c r="V7" s="15"/>
+      <c r="Q7" s="17"/>
+      <c r="R7" s="17"/>
+      <c r="S7" s="17"/>
+      <c r="T7" s="17"/>
+      <c r="U7" s="17"/>
+      <c r="V7" s="17"/>
     </row>
     <row r="8" spans="2:14">
       <c r="B8" s="2"/>
@@ -1476,187 +1535,205 @@
         <v>0</v>
       </c>
       <c r="C9" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E9" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="F9" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G9" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H9" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I9" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J9" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K9" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L9" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="M9" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N9" s="3">
-        <v>0</v>
-      </c>
-      <c r="P9" s="10"/>
-      <c r="Q9" s="13" t="s">
+        <v>-1</v>
+      </c>
+      <c r="P9" s="12"/>
+      <c r="Q9" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="R9" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="S9" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="R9" s="13" t="s">
+      <c r="T9" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="S9" s="13" t="s">
+      <c r="U9" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="T9" s="13" t="s">
+      <c r="V9" s="15" t="s">
         <v>13</v>
-      </c>
-      <c r="U9" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="V9" s="13" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="10" spans="2:22">
       <c r="B10" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="6"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="10">
+        <v>1</v>
+      </c>
+      <c r="F10" s="10">
+        <v>-1</v>
+      </c>
+      <c r="G10" s="10">
+        <v>2</v>
+      </c>
+      <c r="H10" s="10">
+        <v>-1</v>
+      </c>
+      <c r="I10" s="10">
         <v>3</v>
       </c>
-      <c r="C10" s="5"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="8">
-        <v>1</v>
-      </c>
-      <c r="F10" s="8">
-        <v>0</v>
-      </c>
-      <c r="G10" s="8">
-        <v>1</v>
-      </c>
-      <c r="H10" s="8">
-        <v>0</v>
-      </c>
-      <c r="I10" s="8">
-        <v>1</v>
-      </c>
-      <c r="J10" s="8">
-        <v>0</v>
-      </c>
-      <c r="K10" s="8">
-        <v>1</v>
-      </c>
-      <c r="L10" s="8">
-        <v>0</v>
-      </c>
-      <c r="M10" s="8">
-        <v>1</v>
-      </c>
-      <c r="N10" s="8">
-        <v>0</v>
-      </c>
-      <c r="P10" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q10" s="8">
-        <v>0</v>
-      </c>
-      <c r="R10" s="8">
-        <v>0</v>
-      </c>
-      <c r="S10" s="8">
-        <v>0</v>
-      </c>
-      <c r="T10" s="8">
-        <v>0</v>
-      </c>
-      <c r="U10" s="8">
-        <v>0</v>
-      </c>
-      <c r="V10" s="8">
+      <c r="J10" s="10">
+        <v>-1</v>
+      </c>
+      <c r="K10" s="10">
+        <v>4</v>
+      </c>
+      <c r="L10" s="10">
+        <v>-1</v>
+      </c>
+      <c r="M10" s="10">
+        <v>5</v>
+      </c>
+      <c r="N10" s="10">
+        <v>-1</v>
+      </c>
+      <c r="P10" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q10" s="10">
+        <v>0</v>
+      </c>
+      <c r="R10" s="10">
+        <v>0</v>
+      </c>
+      <c r="S10" s="10">
+        <v>0</v>
+      </c>
+      <c r="T10" s="10">
+        <v>0</v>
+      </c>
+      <c r="U10" s="10">
+        <v>0</v>
+      </c>
+      <c r="V10" s="10">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="2:22">
       <c r="B11" s="3" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="9"/>
-      <c r="J11" s="9"/>
-      <c r="K11" s="9"/>
-      <c r="L11" s="9"/>
-      <c r="M11" s="9"/>
-      <c r="N11" s="9"/>
-      <c r="P11" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q11" s="15">
-        <v>0</v>
-      </c>
-      <c r="R11" s="15"/>
-      <c r="S11" s="15"/>
-      <c r="T11" s="15"/>
-      <c r="U11" s="15"/>
-      <c r="V11" s="15"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="11">
+        <v>1</v>
+      </c>
+      <c r="I11" s="11">
+        <v>3</v>
+      </c>
+      <c r="J11" s="11">
+        <v>1</v>
+      </c>
+      <c r="K11" s="11">
+        <v>4</v>
+      </c>
+      <c r="L11" s="11">
+        <v>3</v>
+      </c>
+      <c r="M11" s="11">
+        <v>2</v>
+      </c>
+      <c r="N11" s="11">
+        <v>-1</v>
+      </c>
+      <c r="P11" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q11" s="17">
+        <v>0</v>
+      </c>
+      <c r="R11" s="17"/>
+      <c r="S11" s="17"/>
+      <c r="T11" s="17"/>
+      <c r="U11" s="17"/>
+      <c r="V11" s="17"/>
     </row>
     <row r="12" spans="2:22">
       <c r="B12" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
-      <c r="J12" s="4"/>
-      <c r="K12" s="4"/>
-      <c r="L12" s="4"/>
-      <c r="M12" s="9"/>
-      <c r="N12" s="9"/>
-      <c r="P12" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="6"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="7"/>
+      <c r="J12" s="7"/>
+      <c r="K12" s="7"/>
+      <c r="L12" s="7"/>
+      <c r="M12" s="11">
+        <v>1</v>
+      </c>
+      <c r="N12" s="11">
+        <v>-1</v>
+      </c>
+      <c r="P12" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q12" s="17">
+        <v>0</v>
+      </c>
+      <c r="R12" s="17"/>
+      <c r="S12" s="17"/>
+      <c r="T12" s="17"/>
+      <c r="U12" s="17"/>
+      <c r="V12" s="17"/>
+    </row>
+    <row r="13" spans="16:22">
+      <c r="P13" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="Q12" s="15">
-        <v>0</v>
-      </c>
-      <c r="R12" s="15"/>
-      <c r="S12" s="15"/>
-      <c r="T12" s="15"/>
-      <c r="U12" s="15"/>
-      <c r="V12" s="15"/>
-    </row>
-    <row r="13" spans="16:22">
-      <c r="P13" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q13" s="15">
-        <v>0</v>
-      </c>
-      <c r="R13" s="15"/>
-      <c r="S13" s="15"/>
-      <c r="T13" s="15"/>
-      <c r="U13" s="15"/>
-      <c r="V13" s="15"/>
+      <c r="Q13" s="17">
+        <v>0</v>
+      </c>
+      <c r="R13" s="17"/>
+      <c r="S13" s="17"/>
+      <c r="T13" s="17"/>
+      <c r="U13" s="17"/>
+      <c r="V13" s="17"/>
     </row>
     <row r="14" spans="2:22">
       <c r="B14" s="2"/>
@@ -1696,13 +1773,13 @@
       <c r="N14" s="2">
         <v>11</v>
       </c>
-      <c r="P14" s="12"/>
-      <c r="Q14" s="16"/>
-      <c r="R14" s="16"/>
-      <c r="S14" s="16"/>
-      <c r="T14" s="16"/>
-      <c r="U14" s="16"/>
-      <c r="V14" s="16"/>
+      <c r="P14" s="14"/>
+      <c r="Q14" s="18"/>
+      <c r="R14" s="18"/>
+      <c r="S14" s="18"/>
+      <c r="T14" s="18"/>
+      <c r="U14" s="18"/>
+      <c r="V14" s="18"/>
     </row>
     <row r="15" spans="2:22">
       <c r="B15" s="3" t="s">
@@ -1744,266 +1821,368 @@
       <c r="N15" s="3">
         <v>0</v>
       </c>
-      <c r="P15" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q15" s="13">
-        <v>0</v>
-      </c>
-      <c r="R15" s="13">
-        <v>1</v>
-      </c>
-      <c r="S15" s="13">
-        <v>2</v>
-      </c>
-      <c r="T15" s="13">
+      <c r="P15" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q15" s="15">
+        <v>0</v>
+      </c>
+      <c r="R15" s="15">
+        <v>1</v>
+      </c>
+      <c r="S15" s="15">
+        <v>2</v>
+      </c>
+      <c r="T15" s="15">
         <v>3</v>
       </c>
-      <c r="U15" s="13">
+      <c r="U15" s="15">
         <v>4</v>
       </c>
-      <c r="V15" s="21"/>
+      <c r="V15" s="23"/>
     </row>
     <row r="16" spans="2:22">
       <c r="B16" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" s="6"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="10">
+        <v>1</v>
+      </c>
+      <c r="F16" s="10">
+        <v>0</v>
+      </c>
+      <c r="G16" s="10">
+        <v>2</v>
+      </c>
+      <c r="H16" s="10">
+        <v>0</v>
+      </c>
+      <c r="I16" s="10">
         <v>3</v>
       </c>
-      <c r="C16" s="5"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="8">
-        <v>1</v>
-      </c>
-      <c r="F16" s="8">
-        <v>0</v>
-      </c>
-      <c r="G16" s="8">
-        <v>1</v>
-      </c>
-      <c r="H16" s="8">
-        <v>0</v>
-      </c>
-      <c r="I16" s="8">
-        <v>1</v>
-      </c>
-      <c r="J16" s="8">
-        <v>0</v>
-      </c>
-      <c r="K16" s="8">
-        <v>1</v>
-      </c>
-      <c r="L16" s="8">
-        <v>0</v>
-      </c>
-      <c r="M16" s="8">
-        <v>1</v>
-      </c>
-      <c r="N16" s="8">
-        <v>0</v>
-      </c>
-      <c r="P16" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="8">
-        <v>1</v>
-      </c>
-      <c r="R16" s="8"/>
-      <c r="S16" s="8"/>
-      <c r="T16" s="8"/>
-      <c r="U16" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="V16" s="23"/>
+      <c r="J16" s="10">
+        <v>0</v>
+      </c>
+      <c r="K16" s="10">
+        <v>4</v>
+      </c>
+      <c r="L16" s="10">
+        <v>0</v>
+      </c>
+      <c r="M16" s="10">
+        <v>5</v>
+      </c>
+      <c r="N16" s="10">
+        <v>0</v>
+      </c>
+      <c r="P16" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="10">
+        <v>1</v>
+      </c>
+      <c r="R16" s="10"/>
+      <c r="S16" s="10"/>
+      <c r="T16" s="10"/>
+      <c r="U16" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="V16" s="25"/>
     </row>
     <row r="17" spans="2:22">
       <c r="B17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C17" s="5"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="8">
-        <v>1</v>
-      </c>
-      <c r="I17" s="8">
-        <v>1</v>
-      </c>
-      <c r="J17" s="8">
-        <v>1</v>
-      </c>
-      <c r="K17" s="8">
-        <v>1</v>
-      </c>
-      <c r="L17" s="8">
-        <v>1</v>
-      </c>
-      <c r="M17" s="8">
-        <v>2</v>
-      </c>
-      <c r="N17" s="8">
-        <v>1</v>
-      </c>
-      <c r="P17" s="11">
-        <v>1</v>
-      </c>
-      <c r="Q17" s="15"/>
-      <c r="R17" s="15">
-        <v>1</v>
-      </c>
-      <c r="S17" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="T17" s="17"/>
-      <c r="U17" s="15"/>
-      <c r="V17" s="16"/>
+        <v>15</v>
+      </c>
+      <c r="C17" s="6"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="10">
+        <v>1</v>
+      </c>
+      <c r="I17" s="10">
+        <v>1</v>
+      </c>
+      <c r="J17" s="10">
+        <v>1</v>
+      </c>
+      <c r="K17" s="10">
+        <v>1</v>
+      </c>
+      <c r="L17" s="10">
+        <v>1</v>
+      </c>
+      <c r="M17" s="10">
+        <v>2</v>
+      </c>
+      <c r="N17" s="10">
+        <v>1</v>
+      </c>
+      <c r="P17" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q17" s="17"/>
+      <c r="R17" s="17">
+        <v>1</v>
+      </c>
+      <c r="S17" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="T17" s="19"/>
+      <c r="U17" s="17"/>
+      <c r="V17" s="18"/>
     </row>
     <row r="18" spans="2:22">
       <c r="B18" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" s="6"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="9"/>
+      <c r="I18" s="9"/>
+      <c r="J18" s="9"/>
+      <c r="K18" s="9"/>
+      <c r="L18" s="8"/>
+      <c r="M18" s="10">
+        <v>3</v>
+      </c>
+      <c r="N18" s="10">
+        <v>1</v>
+      </c>
+      <c r="P18" s="13">
+        <v>2</v>
+      </c>
+      <c r="Q18" s="17"/>
+      <c r="R18" s="3"/>
+      <c r="S18" s="17">
+        <v>1</v>
+      </c>
+      <c r="T18" s="17"/>
+      <c r="U18" s="17"/>
+      <c r="V18" s="18"/>
+    </row>
+    <row r="19" spans="16:22">
+      <c r="P19" s="13">
+        <v>3</v>
+      </c>
+      <c r="Q19" s="17"/>
+      <c r="R19" s="3"/>
+      <c r="S19" s="17"/>
+      <c r="T19" s="17">
+        <v>1</v>
+      </c>
+      <c r="U19" s="17"/>
+      <c r="V19" s="18"/>
+    </row>
+    <row r="20" spans="16:22">
+      <c r="P20" s="13">
+        <v>4</v>
+      </c>
+      <c r="Q20" s="17"/>
+      <c r="R20" s="17"/>
+      <c r="S20" s="17"/>
+      <c r="T20" s="17"/>
+      <c r="U20" s="17">
+        <v>1</v>
+      </c>
+      <c r="V20" s="18"/>
+    </row>
+    <row r="21" spans="16:22">
+      <c r="P21" s="14"/>
+      <c r="Q21" s="18"/>
+      <c r="R21" s="18"/>
+      <c r="S21" s="18"/>
+      <c r="T21" s="18"/>
+      <c r="U21" s="18"/>
+      <c r="V21" s="18"/>
+    </row>
+    <row r="22" spans="16:21">
+      <c r="P22" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q22" s="15">
+        <v>0</v>
+      </c>
+      <c r="R22" s="15">
+        <v>1</v>
+      </c>
+      <c r="S22" s="15">
+        <v>2</v>
+      </c>
+      <c r="T22" s="15">
+        <v>3</v>
+      </c>
+      <c r="U22" s="23"/>
+    </row>
+    <row r="23" spans="16:21">
+      <c r="P23" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="R23" s="10"/>
+      <c r="S23" s="10"/>
+      <c r="T23" s="10"/>
+      <c r="U23" s="26"/>
+    </row>
+    <row r="24" spans="16:21">
+      <c r="P24" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q24" s="17"/>
+      <c r="R24" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="S24" s="19"/>
+      <c r="T24" s="19"/>
+      <c r="U24" s="18"/>
+    </row>
+    <row r="25" spans="16:21">
+      <c r="P25" s="13">
+        <v>2</v>
+      </c>
+      <c r="Q25" s="17"/>
+      <c r="R25" s="3"/>
+      <c r="S25" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="T25" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="U25" s="18"/>
+    </row>
+    <row r="26" spans="16:21">
+      <c r="P26" s="13">
+        <v>3</v>
+      </c>
+      <c r="Q26" s="17"/>
+      <c r="R26" s="3"/>
+      <c r="S26" s="17"/>
+      <c r="T26" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="U26" s="18"/>
+    </row>
+    <row r="27" spans="16:21">
+      <c r="P27" s="14"/>
+      <c r="Q27" s="18"/>
+      <c r="R27" s="18"/>
+      <c r="S27" s="18"/>
+      <c r="T27" s="18"/>
+      <c r="U27" s="18"/>
+    </row>
+    <row r="28" spans="16:22">
+      <c r="P28" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q28" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="R28" s="15">
+        <v>1</v>
+      </c>
+      <c r="S28" s="15">
+        <v>2</v>
+      </c>
+      <c r="T28" s="15">
+        <v>3</v>
+      </c>
+      <c r="U28" s="15">
+        <v>2</v>
+      </c>
+      <c r="V28" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="16:22">
+      <c r="P29" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="10"/>
+      <c r="R29" s="10"/>
+      <c r="S29" s="10"/>
+      <c r="T29" s="10"/>
+      <c r="U29" s="10"/>
+      <c r="V29" s="10"/>
+    </row>
+    <row r="30" spans="16:22">
+      <c r="P30" s="12">
+        <v>3</v>
+      </c>
+      <c r="Q30" s="17"/>
+      <c r="R30" s="17"/>
+      <c r="S30" s="17"/>
+      <c r="T30" s="17">
+        <v>1</v>
+      </c>
+      <c r="U30" s="17"/>
+      <c r="V30" s="17"/>
+    </row>
+    <row r="31" spans="16:22">
+      <c r="P31" s="12">
+        <v>2</v>
+      </c>
+      <c r="Q31" s="17"/>
+      <c r="R31" s="17"/>
+      <c r="S31" s="17">
+        <v>1</v>
+      </c>
+      <c r="T31" s="17"/>
+      <c r="U31" s="17">
+        <v>1</v>
+      </c>
+      <c r="V31" s="17"/>
+    </row>
+    <row r="32" spans="16:22">
+      <c r="P32" s="12">
+        <v>1</v>
+      </c>
+      <c r="Q32" s="17"/>
+      <c r="R32" s="17">
+        <v>1</v>
+      </c>
+      <c r="S32" s="17"/>
+      <c r="T32" s="17"/>
+      <c r="U32" s="17"/>
+      <c r="V32" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="16:22">
+      <c r="P33" s="12">
         <v>7</v>
       </c>
-      <c r="C18" s="5"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
-      <c r="I18" s="7"/>
-      <c r="J18" s="7"/>
-      <c r="K18" s="7"/>
-      <c r="L18" s="6"/>
-      <c r="M18" s="8">
-        <v>3</v>
-      </c>
-      <c r="N18" s="8">
-        <v>1</v>
-      </c>
-      <c r="P18" s="11">
-        <v>2</v>
-      </c>
-      <c r="Q18" s="15"/>
-      <c r="R18" s="3"/>
-      <c r="S18" s="15">
-        <v>1</v>
-      </c>
-      <c r="T18" s="15"/>
-      <c r="U18" s="15"/>
-      <c r="V18" s="16"/>
-    </row>
-    <row r="19" spans="16:22">
-      <c r="P19" s="11">
-        <v>3</v>
-      </c>
-      <c r="Q19" s="15"/>
-      <c r="R19" s="3"/>
-      <c r="S19" s="15"/>
-      <c r="T19" s="15">
-        <v>1</v>
-      </c>
-      <c r="U19" s="15"/>
-      <c r="V19" s="16"/>
-    </row>
-    <row r="20" spans="16:22">
-      <c r="P20" s="11">
+      <c r="Q33" s="17"/>
+      <c r="R33" s="17"/>
+      <c r="S33" s="17"/>
+      <c r="T33" s="17"/>
+      <c r="U33" s="17"/>
+      <c r="V33" s="17"/>
+    </row>
+    <row r="34" spans="16:22">
+      <c r="P34" s="12">
         <v>4</v>
       </c>
-      <c r="Q20" s="15"/>
-      <c r="R20" s="15"/>
-      <c r="S20" s="15"/>
-      <c r="T20" s="15"/>
-      <c r="U20" s="15">
-        <v>1</v>
-      </c>
-      <c r="V20" s="16"/>
-    </row>
-    <row r="21" spans="16:22">
-      <c r="P21" s="12"/>
-      <c r="Q21" s="16"/>
-      <c r="R21" s="16"/>
-      <c r="S21" s="16"/>
-      <c r="T21" s="16"/>
-      <c r="U21" s="16"/>
-      <c r="V21" s="16"/>
-    </row>
-    <row r="22" spans="16:21">
-      <c r="P22" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q22" s="13">
-        <v>0</v>
-      </c>
-      <c r="R22" s="13">
-        <v>1</v>
-      </c>
-      <c r="S22" s="13">
-        <v>2</v>
-      </c>
-      <c r="T22" s="13">
-        <v>3</v>
-      </c>
-      <c r="U22" s="24"/>
-    </row>
-    <row r="23" spans="16:21">
-      <c r="P23" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q23" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="R23" s="8"/>
-      <c r="S23" s="8"/>
-      <c r="T23" s="8"/>
-      <c r="U23" s="25"/>
-    </row>
-    <row r="24" spans="16:21">
-      <c r="P24" s="11">
-        <v>1</v>
-      </c>
-      <c r="Q24" s="15"/>
-      <c r="R24" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="S24" s="17"/>
-      <c r="T24" s="17"/>
-      <c r="U24" s="16"/>
-    </row>
-    <row r="25" spans="16:21">
-      <c r="P25" s="11">
-        <v>2</v>
-      </c>
-      <c r="Q25" s="15"/>
-      <c r="R25" s="3"/>
-      <c r="S25" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="T25" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="U25" s="16"/>
-    </row>
-    <row r="26" spans="16:21">
-      <c r="P26" s="11">
-        <v>3</v>
-      </c>
-      <c r="Q26" s="15"/>
-      <c r="R26" s="3"/>
-      <c r="S26" s="15"/>
-      <c r="T26" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="U26" s="16"/>
-    </row>
-    <row r="27" spans="16:21">
-      <c r="P27" s="12"/>
-      <c r="Q27" s="16"/>
-      <c r="R27" s="16"/>
-      <c r="S27" s="16"/>
-      <c r="T27" s="16"/>
-      <c r="U27" s="16"/>
+      <c r="Q34" s="17"/>
+      <c r="R34" s="17"/>
+      <c r="S34" s="17"/>
+      <c r="T34" s="17"/>
+      <c r="U34" s="17"/>
+      <c r="V34" s="17"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="7">
+    <mergeCell ref="C6:G6"/>
     <mergeCell ref="C10:D10"/>
+    <mergeCell ref="D11:G11"/>
+    <mergeCell ref="C12:L12"/>
     <mergeCell ref="C16:D16"/>
     <mergeCell ref="C17:G17"/>
     <mergeCell ref="C18:L18"/>

--- a/leetcode/dptable.xlsx
+++ b/leetcode/dptable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28000" windowHeight="12580"/>
+    <workbookView windowWidth="28800" windowHeight="12580"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21">
   <si>
     <t>[]</t>
   </si>
@@ -25,19 +25,13 @@
     <t>F</t>
   </si>
   <si>
-    <t>[2]</t>
-  </si>
-  <si>
     <t>[1]</t>
-  </si>
-  <si>
-    <t>[2, 5]</t>
   </si>
   <si>
     <t>[1, 2]</t>
   </si>
   <si>
-    <t>[2, 5, 10]</t>
+    <t>[1, 2, 5]</t>
   </si>
   <si>
     <t>[1, 2, 3]</t>
@@ -64,6 +58,15 @@
     <t>e</t>
   </si>
   <si>
+    <t>[2]</t>
+  </si>
+  <si>
+    <t>[2, 5]</t>
+  </si>
+  <si>
+    <t>[2, 5, 10]</t>
+  </si>
+  <si>
     <t>abcbe</t>
   </si>
   <si>
@@ -81,9 +84,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="24">
@@ -117,6 +120,29 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -135,13 +161,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="15"/>
       <color theme="3"/>
@@ -158,53 +177,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -217,10 +194,68 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -231,38 +266,6 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="34">
     <fill>
@@ -291,169 +294,169 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -544,21 +547,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
@@ -569,15 +557,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -597,6 +576,41 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -611,168 +625,157 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="24" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -785,12 +788,18 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="42" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="42" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="42" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="42" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="42" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="42" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -843,9 +852,6 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="18" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1221,216 +1227,266 @@
       <c r="N2" s="2">
         <v>11</v>
       </c>
-      <c r="P2" s="10"/>
-      <c r="Q2" s="13">
-        <v>0</v>
-      </c>
-      <c r="R2" s="13">
-        <v>1</v>
-      </c>
-      <c r="S2" s="13">
-        <v>2</v>
-      </c>
-      <c r="T2" s="13">
+      <c r="P2" s="12"/>
+      <c r="Q2" s="15">
+        <v>0</v>
+      </c>
+      <c r="R2" s="15">
+        <v>1</v>
+      </c>
+      <c r="S2" s="15">
+        <v>2</v>
+      </c>
+      <c r="T2" s="15">
         <v>3</v>
       </c>
-      <c r="U2" s="13">
+      <c r="U2" s="15">
         <v>4</v>
       </c>
-      <c r="V2" s="13">
+      <c r="V2" s="15">
         <v>5</v>
       </c>
-      <c r="W2" s="18"/>
-      <c r="X2" s="18"/>
-      <c r="Y2" s="18"/>
-      <c r="Z2" s="18"/>
-      <c r="AA2" s="18"/>
-      <c r="AB2" s="18"/>
+      <c r="W2" s="20"/>
+      <c r="X2" s="20"/>
+      <c r="Y2" s="20"/>
+      <c r="Z2" s="20"/>
+      <c r="AA2" s="20"/>
+      <c r="AB2" s="20"/>
     </row>
     <row r="3" spans="2:28">
       <c r="B3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C3" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E3" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="F3" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G3" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H3" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I3" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J3" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K3" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L3" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="M3" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N3" s="3">
-        <v>0</v>
-      </c>
-      <c r="P3" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="R3" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="S3" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="T3" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="U3" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="V3" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="W3" s="19"/>
-      <c r="X3" s="19"/>
-      <c r="Y3" s="19"/>
-      <c r="Z3" s="19"/>
-      <c r="AA3" s="19"/>
-      <c r="AB3" s="19"/>
+        <v>-1</v>
+      </c>
+      <c r="P3" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="R3" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="S3" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="T3" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="U3" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="V3" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="W3" s="21"/>
+      <c r="X3" s="21"/>
+      <c r="Y3" s="21"/>
+      <c r="Z3" s="21"/>
+      <c r="AA3" s="21"/>
+      <c r="AB3" s="21"/>
     </row>
     <row r="4" spans="2:28">
       <c r="B4" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
-      <c r="M4" s="4"/>
-      <c r="N4" s="4"/>
-      <c r="P4" s="11" t="s">
+      <c r="D4" s="3">
+        <v>1</v>
+      </c>
+      <c r="E4" s="10">
+        <v>2</v>
+      </c>
+      <c r="F4" s="10">
+        <v>3</v>
+      </c>
+      <c r="G4" s="10">
         <v>4</v>
       </c>
-      <c r="Q4" s="14"/>
-      <c r="R4" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="S4" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="T4" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="U4" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="V4" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="W4" s="20"/>
-      <c r="X4" s="20"/>
-      <c r="Y4" s="20"/>
-      <c r="Z4" s="20"/>
-      <c r="AA4" s="20"/>
-      <c r="AB4" s="20"/>
+      <c r="H4" s="10">
+        <v>5</v>
+      </c>
+      <c r="I4" s="10">
+        <v>6</v>
+      </c>
+      <c r="J4" s="10">
+        <v>7</v>
+      </c>
+      <c r="K4" s="10">
+        <v>8</v>
+      </c>
+      <c r="L4" s="10">
+        <v>9</v>
+      </c>
+      <c r="M4" s="10">
+        <v>10</v>
+      </c>
+      <c r="N4" s="10">
+        <v>11</v>
+      </c>
+      <c r="P4" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q4" s="16"/>
+      <c r="R4" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="S4" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="T4" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="U4" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="V4" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="W4" s="22"/>
+      <c r="X4" s="22"/>
+      <c r="Y4" s="22"/>
+      <c r="Z4" s="22"/>
+      <c r="AA4" s="22"/>
+      <c r="AB4" s="22"/>
     </row>
     <row r="5" spans="2:28">
       <c r="B5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="3">
+        <v>1</v>
+      </c>
+      <c r="F5" s="3">
+        <v>2</v>
+      </c>
+      <c r="G5" s="3">
+        <v>2</v>
+      </c>
+      <c r="H5" s="11">
+        <v>3</v>
+      </c>
+      <c r="I5" s="11">
+        <v>3</v>
+      </c>
+      <c r="J5" s="11">
+        <v>4</v>
+      </c>
+      <c r="K5" s="11">
+        <v>4</v>
+      </c>
+      <c r="L5" s="11">
         <v>5</v>
       </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
-      <c r="K5" s="4"/>
-      <c r="L5" s="4"/>
-      <c r="M5" s="4"/>
-      <c r="N5" s="4"/>
-      <c r="P5" s="11" t="s">
+      <c r="M5" s="11">
+        <v>5</v>
+      </c>
+      <c r="N5" s="11">
         <v>6</v>
       </c>
-      <c r="Q5" s="15"/>
-      <c r="R5" s="15"/>
-      <c r="S5" s="15"/>
-      <c r="T5" s="15"/>
-      <c r="U5" s="15"/>
-      <c r="V5" s="15"/>
-      <c r="W5" s="20"/>
-      <c r="X5" s="20"/>
-      <c r="Y5" s="20"/>
-      <c r="Z5" s="20"/>
-      <c r="AA5" s="20"/>
-      <c r="AB5" s="20"/>
+      <c r="P5" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q5" s="17"/>
+      <c r="R5" s="17"/>
+      <c r="S5" s="17"/>
+      <c r="T5" s="17"/>
+      <c r="U5" s="17"/>
+      <c r="V5" s="17"/>
+      <c r="W5" s="22"/>
+      <c r="X5" s="22"/>
+      <c r="Y5" s="22"/>
+      <c r="Z5" s="22"/>
+      <c r="AA5" s="22"/>
+      <c r="AB5" s="22"/>
     </row>
     <row r="6" spans="2:28">
       <c r="B6" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="6"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="10">
+        <v>1</v>
+      </c>
+      <c r="I6" s="10">
+        <v>2</v>
+      </c>
+      <c r="J6" s="10">
+        <v>2</v>
+      </c>
+      <c r="K6" s="10">
+        <v>3</v>
+      </c>
+      <c r="L6" s="10"/>
+      <c r="M6" s="11"/>
+      <c r="N6" s="11"/>
+      <c r="P6" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q6" s="17"/>
+      <c r="R6" s="17"/>
+      <c r="S6" s="17"/>
+      <c r="T6" s="17"/>
+      <c r="U6" s="17"/>
+      <c r="V6" s="17"/>
+      <c r="W6" s="22"/>
+      <c r="X6" s="22"/>
+      <c r="Y6" s="22"/>
+      <c r="Z6" s="22"/>
+      <c r="AA6" s="22"/>
+      <c r="AB6" s="22"/>
+    </row>
+    <row r="7" spans="16:22">
+      <c r="P7" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
-      <c r="K6" s="4"/>
-      <c r="L6" s="4"/>
-      <c r="M6" s="4"/>
-      <c r="N6" s="4"/>
-      <c r="P6" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q6" s="15"/>
-      <c r="R6" s="15"/>
-      <c r="S6" s="15"/>
-      <c r="T6" s="15"/>
-      <c r="U6" s="15"/>
-      <c r="V6" s="15"/>
-      <c r="W6" s="20"/>
-      <c r="X6" s="20"/>
-      <c r="Y6" s="20"/>
-      <c r="Z6" s="20"/>
-      <c r="AA6" s="20"/>
-      <c r="AB6" s="20"/>
-    </row>
-    <row r="7" spans="16:22">
-      <c r="P7" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q7" s="15"/>
-      <c r="R7" s="15"/>
-      <c r="S7" s="15"/>
-      <c r="T7" s="15"/>
-      <c r="U7" s="15"/>
-      <c r="V7" s="15"/>
+      <c r="Q7" s="17"/>
+      <c r="R7" s="17"/>
+      <c r="S7" s="17"/>
+      <c r="T7" s="17"/>
+      <c r="U7" s="17"/>
+      <c r="V7" s="17"/>
     </row>
     <row r="8" spans="2:14">
       <c r="B8" s="2"/>
@@ -1476,187 +1532,205 @@
         <v>0</v>
       </c>
       <c r="C9" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E9" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="F9" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G9" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H9" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I9" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J9" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K9" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L9" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="M9" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N9" s="3">
-        <v>0</v>
-      </c>
-      <c r="P9" s="10"/>
-      <c r="Q9" s="13" t="s">
+        <v>-1</v>
+      </c>
+      <c r="P9" s="12"/>
+      <c r="Q9" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="R9" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="S9" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="R9" s="13" t="s">
+      <c r="T9" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="S9" s="13" t="s">
+      <c r="U9" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="T9" s="13" t="s">
+      <c r="V9" s="15" t="s">
         <v>13</v>
-      </c>
-      <c r="U9" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="V9" s="13" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="10" spans="2:22">
       <c r="B10" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="6"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="10">
+        <v>1</v>
+      </c>
+      <c r="F10" s="10">
+        <v>-1</v>
+      </c>
+      <c r="G10" s="10">
+        <v>2</v>
+      </c>
+      <c r="H10" s="10">
+        <v>-1</v>
+      </c>
+      <c r="I10" s="10">
         <v>3</v>
       </c>
-      <c r="C10" s="5"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="8">
-        <v>1</v>
-      </c>
-      <c r="F10" s="8">
-        <v>0</v>
-      </c>
-      <c r="G10" s="8">
-        <v>1</v>
-      </c>
-      <c r="H10" s="8">
-        <v>0</v>
-      </c>
-      <c r="I10" s="8">
-        <v>1</v>
-      </c>
-      <c r="J10" s="8">
-        <v>0</v>
-      </c>
-      <c r="K10" s="8">
-        <v>1</v>
-      </c>
-      <c r="L10" s="8">
-        <v>0</v>
-      </c>
-      <c r="M10" s="8">
-        <v>1</v>
-      </c>
-      <c r="N10" s="8">
-        <v>0</v>
-      </c>
-      <c r="P10" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q10" s="8">
-        <v>0</v>
-      </c>
-      <c r="R10" s="8">
-        <v>0</v>
-      </c>
-      <c r="S10" s="8">
-        <v>0</v>
-      </c>
-      <c r="T10" s="8">
-        <v>0</v>
-      </c>
-      <c r="U10" s="8">
-        <v>0</v>
-      </c>
-      <c r="V10" s="8">
+      <c r="J10" s="10">
+        <v>-1</v>
+      </c>
+      <c r="K10" s="10">
+        <v>4</v>
+      </c>
+      <c r="L10" s="10">
+        <v>-1</v>
+      </c>
+      <c r="M10" s="10">
+        <v>5</v>
+      </c>
+      <c r="N10" s="10">
+        <v>-1</v>
+      </c>
+      <c r="P10" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q10" s="10">
+        <v>0</v>
+      </c>
+      <c r="R10" s="10">
+        <v>0</v>
+      </c>
+      <c r="S10" s="10">
+        <v>0</v>
+      </c>
+      <c r="T10" s="10">
+        <v>0</v>
+      </c>
+      <c r="U10" s="10">
+        <v>0</v>
+      </c>
+      <c r="V10" s="10">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="2:22">
       <c r="B11" s="3" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="9"/>
-      <c r="J11" s="9"/>
-      <c r="K11" s="9"/>
-      <c r="L11" s="9"/>
-      <c r="M11" s="9"/>
-      <c r="N11" s="9"/>
-      <c r="P11" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q11" s="15">
-        <v>0</v>
-      </c>
-      <c r="R11" s="15"/>
-      <c r="S11" s="15"/>
-      <c r="T11" s="15"/>
-      <c r="U11" s="15"/>
-      <c r="V11" s="15"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="11">
+        <v>1</v>
+      </c>
+      <c r="I11" s="11">
+        <v>3</v>
+      </c>
+      <c r="J11" s="11">
+        <v>1</v>
+      </c>
+      <c r="K11" s="11">
+        <v>4</v>
+      </c>
+      <c r="L11" s="11">
+        <v>3</v>
+      </c>
+      <c r="M11" s="11">
+        <v>2</v>
+      </c>
+      <c r="N11" s="11">
+        <v>-1</v>
+      </c>
+      <c r="P11" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q11" s="17">
+        <v>0</v>
+      </c>
+      <c r="R11" s="17"/>
+      <c r="S11" s="17"/>
+      <c r="T11" s="17"/>
+      <c r="U11" s="17"/>
+      <c r="V11" s="17"/>
     </row>
     <row r="12" spans="2:22">
       <c r="B12" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
-      <c r="J12" s="4"/>
-      <c r="K12" s="4"/>
-      <c r="L12" s="4"/>
-      <c r="M12" s="9"/>
-      <c r="N12" s="9"/>
-      <c r="P12" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="6"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="7"/>
+      <c r="J12" s="7"/>
+      <c r="K12" s="7"/>
+      <c r="L12" s="7"/>
+      <c r="M12" s="11">
+        <v>1</v>
+      </c>
+      <c r="N12" s="11">
+        <v>-1</v>
+      </c>
+      <c r="P12" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q12" s="17">
+        <v>0</v>
+      </c>
+      <c r="R12" s="17"/>
+      <c r="S12" s="17"/>
+      <c r="T12" s="17"/>
+      <c r="U12" s="17"/>
+      <c r="V12" s="17"/>
+    </row>
+    <row r="13" spans="16:22">
+      <c r="P13" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="Q12" s="15">
-        <v>0</v>
-      </c>
-      <c r="R12" s="15"/>
-      <c r="S12" s="15"/>
-      <c r="T12" s="15"/>
-      <c r="U12" s="15"/>
-      <c r="V12" s="15"/>
-    </row>
-    <row r="13" spans="16:22">
-      <c r="P13" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q13" s="15">
-        <v>0</v>
-      </c>
-      <c r="R13" s="15"/>
-      <c r="S13" s="15"/>
-      <c r="T13" s="15"/>
-      <c r="U13" s="15"/>
-      <c r="V13" s="15"/>
+      <c r="Q13" s="17">
+        <v>0</v>
+      </c>
+      <c r="R13" s="17"/>
+      <c r="S13" s="17"/>
+      <c r="T13" s="17"/>
+      <c r="U13" s="17"/>
+      <c r="V13" s="17"/>
     </row>
     <row r="14" spans="2:22">
       <c r="B14" s="2"/>
@@ -1696,13 +1770,13 @@
       <c r="N14" s="2">
         <v>11</v>
       </c>
-      <c r="P14" s="12"/>
-      <c r="Q14" s="16"/>
-      <c r="R14" s="16"/>
-      <c r="S14" s="16"/>
-      <c r="T14" s="16"/>
-      <c r="U14" s="16"/>
-      <c r="V14" s="16"/>
+      <c r="P14" s="14"/>
+      <c r="Q14" s="18"/>
+      <c r="R14" s="18"/>
+      <c r="S14" s="18"/>
+      <c r="T14" s="18"/>
+      <c r="U14" s="18"/>
+      <c r="V14" s="18"/>
     </row>
     <row r="15" spans="2:22">
       <c r="B15" s="3" t="s">
@@ -1744,266 +1818,269 @@
       <c r="N15" s="3">
         <v>0</v>
       </c>
-      <c r="P15" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q15" s="13">
-        <v>0</v>
-      </c>
-      <c r="R15" s="13">
-        <v>1</v>
-      </c>
-      <c r="S15" s="13">
-        <v>2</v>
-      </c>
-      <c r="T15" s="13">
+      <c r="P15" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q15" s="15">
+        <v>0</v>
+      </c>
+      <c r="R15" s="15">
+        <v>1</v>
+      </c>
+      <c r="S15" s="15">
+        <v>2</v>
+      </c>
+      <c r="T15" s="15">
         <v>3</v>
       </c>
-      <c r="U15" s="13">
+      <c r="U15" s="15">
         <v>4</v>
       </c>
-      <c r="V15" s="21"/>
+      <c r="V15" s="23"/>
     </row>
     <row r="16" spans="2:22">
       <c r="B16" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" s="6"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="10">
+        <v>1</v>
+      </c>
+      <c r="F16" s="10">
+        <v>0</v>
+      </c>
+      <c r="G16" s="10">
+        <v>2</v>
+      </c>
+      <c r="H16" s="10">
+        <v>0</v>
+      </c>
+      <c r="I16" s="10">
         <v>3</v>
       </c>
-      <c r="C16" s="5"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="8">
-        <v>1</v>
-      </c>
-      <c r="F16" s="8">
-        <v>0</v>
-      </c>
-      <c r="G16" s="8">
-        <v>1</v>
-      </c>
-      <c r="H16" s="8">
-        <v>0</v>
-      </c>
-      <c r="I16" s="8">
-        <v>1</v>
-      </c>
-      <c r="J16" s="8">
-        <v>0</v>
-      </c>
-      <c r="K16" s="8">
-        <v>1</v>
-      </c>
-      <c r="L16" s="8">
-        <v>0</v>
-      </c>
-      <c r="M16" s="8">
-        <v>1</v>
-      </c>
-      <c r="N16" s="8">
-        <v>0</v>
-      </c>
-      <c r="P16" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="8">
-        <v>1</v>
-      </c>
-      <c r="R16" s="8"/>
-      <c r="S16" s="8"/>
-      <c r="T16" s="8"/>
-      <c r="U16" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="V16" s="23"/>
+      <c r="J16" s="10">
+        <v>0</v>
+      </c>
+      <c r="K16" s="10">
+        <v>4</v>
+      </c>
+      <c r="L16" s="10">
+        <v>0</v>
+      </c>
+      <c r="M16" s="10">
+        <v>5</v>
+      </c>
+      <c r="N16" s="10">
+        <v>0</v>
+      </c>
+      <c r="P16" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="10">
+        <v>1</v>
+      </c>
+      <c r="R16" s="10"/>
+      <c r="S16" s="10"/>
+      <c r="T16" s="10"/>
+      <c r="U16" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="V16" s="25"/>
     </row>
     <row r="17" spans="2:22">
       <c r="B17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C17" s="5"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="8">
-        <v>1</v>
-      </c>
-      <c r="I17" s="8">
-        <v>1</v>
-      </c>
-      <c r="J17" s="8">
-        <v>1</v>
-      </c>
-      <c r="K17" s="8">
-        <v>1</v>
-      </c>
-      <c r="L17" s="8">
-        <v>1</v>
-      </c>
-      <c r="M17" s="8">
-        <v>2</v>
-      </c>
-      <c r="N17" s="8">
-        <v>1</v>
-      </c>
-      <c r="P17" s="11">
-        <v>1</v>
-      </c>
-      <c r="Q17" s="15"/>
-      <c r="R17" s="15">
-        <v>1</v>
-      </c>
-      <c r="S17" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="T17" s="17"/>
-      <c r="U17" s="15"/>
-      <c r="V17" s="16"/>
+        <v>15</v>
+      </c>
+      <c r="C17" s="6"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="10">
+        <v>1</v>
+      </c>
+      <c r="I17" s="10">
+        <v>1</v>
+      </c>
+      <c r="J17" s="10">
+        <v>1</v>
+      </c>
+      <c r="K17" s="10">
+        <v>1</v>
+      </c>
+      <c r="L17" s="10">
+        <v>1</v>
+      </c>
+      <c r="M17" s="10">
+        <v>2</v>
+      </c>
+      <c r="N17" s="10">
+        <v>1</v>
+      </c>
+      <c r="P17" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q17" s="17"/>
+      <c r="R17" s="17">
+        <v>1</v>
+      </c>
+      <c r="S17" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="T17" s="19"/>
+      <c r="U17" s="17"/>
+      <c r="V17" s="18"/>
     </row>
     <row r="18" spans="2:22">
       <c r="B18" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C18" s="5"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
-      <c r="I18" s="7"/>
-      <c r="J18" s="7"/>
-      <c r="K18" s="7"/>
-      <c r="L18" s="6"/>
-      <c r="M18" s="8">
+        <v>16</v>
+      </c>
+      <c r="C18" s="6"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="9"/>
+      <c r="I18" s="9"/>
+      <c r="J18" s="9"/>
+      <c r="K18" s="9"/>
+      <c r="L18" s="8"/>
+      <c r="M18" s="10">
         <v>3</v>
       </c>
-      <c r="N18" s="8">
-        <v>1</v>
-      </c>
-      <c r="P18" s="11">
-        <v>2</v>
-      </c>
-      <c r="Q18" s="15"/>
+      <c r="N18" s="10">
+        <v>1</v>
+      </c>
+      <c r="P18" s="13">
+        <v>2</v>
+      </c>
+      <c r="Q18" s="17"/>
       <c r="R18" s="3"/>
-      <c r="S18" s="15">
-        <v>1</v>
-      </c>
-      <c r="T18" s="15"/>
-      <c r="U18" s="15"/>
-      <c r="V18" s="16"/>
+      <c r="S18" s="17">
+        <v>1</v>
+      </c>
+      <c r="T18" s="17"/>
+      <c r="U18" s="17"/>
+      <c r="V18" s="18"/>
     </row>
     <row r="19" spans="16:22">
-      <c r="P19" s="11">
+      <c r="P19" s="13">
         <v>3</v>
       </c>
-      <c r="Q19" s="15"/>
+      <c r="Q19" s="17"/>
       <c r="R19" s="3"/>
-      <c r="S19" s="15"/>
-      <c r="T19" s="15">
-        <v>1</v>
-      </c>
-      <c r="U19" s="15"/>
-      <c r="V19" s="16"/>
+      <c r="S19" s="17"/>
+      <c r="T19" s="17">
+        <v>1</v>
+      </c>
+      <c r="U19" s="17"/>
+      <c r="V19" s="18"/>
     </row>
     <row r="20" spans="16:22">
-      <c r="P20" s="11">
+      <c r="P20" s="13">
         <v>4</v>
       </c>
-      <c r="Q20" s="15"/>
-      <c r="R20" s="15"/>
-      <c r="S20" s="15"/>
-      <c r="T20" s="15"/>
-      <c r="U20" s="15">
-        <v>1</v>
-      </c>
-      <c r="V20" s="16"/>
+      <c r="Q20" s="17"/>
+      <c r="R20" s="17"/>
+      <c r="S20" s="17"/>
+      <c r="T20" s="17"/>
+      <c r="U20" s="17">
+        <v>1</v>
+      </c>
+      <c r="V20" s="18"/>
     </row>
     <row r="21" spans="16:22">
-      <c r="P21" s="12"/>
-      <c r="Q21" s="16"/>
-      <c r="R21" s="16"/>
-      <c r="S21" s="16"/>
-      <c r="T21" s="16"/>
-      <c r="U21" s="16"/>
-      <c r="V21" s="16"/>
+      <c r="P21" s="14"/>
+      <c r="Q21" s="18"/>
+      <c r="R21" s="18"/>
+      <c r="S21" s="18"/>
+      <c r="T21" s="18"/>
+      <c r="U21" s="18"/>
+      <c r="V21" s="18"/>
     </row>
     <row r="22" spans="16:21">
-      <c r="P22" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q22" s="13">
-        <v>0</v>
-      </c>
-      <c r="R22" s="13">
-        <v>1</v>
-      </c>
-      <c r="S22" s="13">
-        <v>2</v>
-      </c>
-      <c r="T22" s="13">
+      <c r="P22" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q22" s="15">
+        <v>0</v>
+      </c>
+      <c r="R22" s="15">
+        <v>1</v>
+      </c>
+      <c r="S22" s="15">
+        <v>2</v>
+      </c>
+      <c r="T22" s="15">
         <v>3</v>
       </c>
-      <c r="U22" s="24"/>
+      <c r="U22" s="23"/>
     </row>
     <row r="23" spans="16:21">
-      <c r="P23" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q23" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="R23" s="8"/>
-      <c r="S23" s="8"/>
-      <c r="T23" s="8"/>
-      <c r="U23" s="25"/>
+      <c r="P23" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="R23" s="10"/>
+      <c r="S23" s="10"/>
+      <c r="T23" s="10"/>
+      <c r="U23" s="26"/>
     </row>
     <row r="24" spans="16:21">
-      <c r="P24" s="11">
-        <v>1</v>
-      </c>
-      <c r="Q24" s="15"/>
-      <c r="R24" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="S24" s="17"/>
-      <c r="T24" s="17"/>
-      <c r="U24" s="16"/>
+      <c r="P24" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q24" s="17"/>
+      <c r="R24" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="S24" s="19"/>
+      <c r="T24" s="19"/>
+      <c r="U24" s="18"/>
     </row>
     <row r="25" spans="16:21">
-      <c r="P25" s="11">
-        <v>2</v>
-      </c>
-      <c r="Q25" s="15"/>
+      <c r="P25" s="13">
+        <v>2</v>
+      </c>
+      <c r="Q25" s="17"/>
       <c r="R25" s="3"/>
-      <c r="S25" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="T25" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="U25" s="16"/>
+      <c r="S25" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="T25" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="U25" s="18"/>
     </row>
     <row r="26" spans="16:21">
-      <c r="P26" s="11">
+      <c r="P26" s="13">
         <v>3</v>
       </c>
-      <c r="Q26" s="15"/>
+      <c r="Q26" s="17"/>
       <c r="R26" s="3"/>
-      <c r="S26" s="15"/>
-      <c r="T26" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="U26" s="16"/>
+      <c r="S26" s="17"/>
+      <c r="T26" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="U26" s="18"/>
     </row>
     <row r="27" spans="16:21">
-      <c r="P27" s="12"/>
-      <c r="Q27" s="16"/>
-      <c r="R27" s="16"/>
-      <c r="S27" s="16"/>
-      <c r="T27" s="16"/>
-      <c r="U27" s="16"/>
+      <c r="P27" s="14"/>
+      <c r="Q27" s="18"/>
+      <c r="R27" s="18"/>
+      <c r="S27" s="18"/>
+      <c r="T27" s="18"/>
+      <c r="U27" s="18"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="7">
+    <mergeCell ref="C6:G6"/>
     <mergeCell ref="C10:D10"/>
+    <mergeCell ref="D11:G11"/>
+    <mergeCell ref="C12:L12"/>
     <mergeCell ref="C16:D16"/>
     <mergeCell ref="C17:G17"/>
     <mergeCell ref="C18:L18"/>
